--- a/TP2026/TP9.xlsx
+++ b/TP2026/TP9.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahto\OneDrive\Documents\GitHub\u3\TP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834BBB74-51EF-4897-AEC4-478BE5F038DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F49ECA7-9A59-4FD1-8ED0-32655AAD9186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{81613824-27A1-410A-B2DF-370252333762}"/>
   </bookViews>
   <sheets>
-    <sheet name="🌿 Coopérative Argan" sheetId="1" r:id="rId1"/>
+    <sheet name="🌿 Coopérative Argan" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +41,7 @@
     <author>Abdellah TAHTOH</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{E2149996-1691-4DFF-B431-4452BD1CAB89}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{80B75B95-B71C-426A-832B-6742BB61CE33}">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{7C8FAC67-D66F-4E8B-970A-2DA42885EF40}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{178AF00C-2A33-4BF5-A49A-FEBD6761A4DE}">
       <text>
         <r>
           <rPr>
@@ -72,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{5F70C084-FAF6-4C36-9E9E-5127142C5698}">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{4C30C938-704C-4006-82F1-C656CA9B33BF}">
       <text>
         <r>
           <rPr>
@@ -86,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{8BD662CA-7167-40A1-BF7C-E025CA285702}">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{21763D80-4842-4235-A438-9A2A9EC7D2B6}">
       <text>
         <r>
           <rPr>
@@ -100,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{B7CDD864-372D-41FA-9596-27502031C13B}">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{616B2A91-307A-44B6-BFCF-2E00D8019CE3}">
       <text>
         <r>
           <rPr>
@@ -110,11 +110,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>الانتاج</t>
+          <t>الإنتاج في الاسبوع</t>
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{423FDAE8-33CC-4CE9-BA8B-BD9609915893}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{11B4639F-B2A7-4BE6-A869-CC8CA698578C}">
       <text>
         <r>
           <rPr>
@@ -128,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00E2698A-0DCF-4092-852A-6378A6FB74F7}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{0E545F35-B75D-470D-AA30-C86374277BA5}">
       <text>
         <r>
           <rPr>
@@ -142,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{F4C539A0-FA55-442D-8182-64E50C884A4F}">
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{143F4DFC-0549-4469-8B84-F283AAB709DE}">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{3D48DFA4-A1AD-4D50-8B31-E41D732F8616}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{5715D6C7-2331-4B18-83A5-D676C4FD8378}">
       <text>
         <r>
           <rPr>
@@ -170,7 +170,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{EF602834-F910-4654-87A3-9E048FDFE598}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{67B2DEB7-CE3E-4C90-BEA6-EE6AF2E40EA4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">النسبة المؤوية
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{78117FDA-EA81-4980-A3B4-64A084F3F9E6}">
       <text>
         <r>
           <rPr>
@@ -180,17 +194,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>🎯 العمل المطلوب:
-1️⃣ الدخل الأساسي = الإنتاج × الثمن
-2️⃣ منحة بشرط (SI) = إذا كان الدخل الأساسي ≥ 10 → 50 درهم ؛ وإلا → 0 درهم
-3️⃣ الدخل الإجمالي = الدخل الأساسي + المنحة
-4️⃣ إذا أصبحت المنحة 100 درهم عندما يكون الإنتاج ≥ 15 لترًا، قم بتعديل الصيغة.
-5️⃣ كم عدد المنتجات اللواتي حصلن على منحة هذا الأسبوع؟
-6️⃣ ما هو الإنتاج الإجمالي للتعاونية؟</t>
+          <t>إجمالي الدخل الموزع (درهم)</t>
         </r>
       </text>
     </comment>
-    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{CDEFFB7A-F697-49E2-944D-D9D47178CD4E}">
+    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{1CDF085B-3C68-4A91-9F9B-5D2CAF338774}">
       <text>
         <r>
           <rPr>
@@ -204,21 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{A4A97C27-775B-4BC0-91AB-AF85232804B2}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>إجمالي الدخل الموزع (درهم)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{3CDF6EFA-0526-4FA6-B6B9-1BEAE60DD56B}">
+    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{208D4BEA-6FBE-416A-B8C8-46E771CD8B42}">
       <text>
         <r>
           <rPr>
@@ -232,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{A546E164-2884-4437-818B-FF874C466460}">
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{04CC37AE-F388-4FD9-8CE1-1C29568502BA}">
       <text>
         <r>
           <rPr>
@@ -246,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{9E0B277F-B0A9-4ABA-ABF5-7E5E3A5D58A6}">
+    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{CE5AB4CE-167B-481D-8159-E81ADA41A249}">
       <text>
         <r>
           <rPr>
@@ -265,10 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="37">
-  <si>
-    <t>🌿 EXERCICE – Coopérative Arganière de Souss Massa | Fonction SI</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="36">
   <si>
     <t>Situation : Tu travailles dans une coopérative d'huile d'argan dans la région de Souss Massa. Les productrices reçoivent une prime si leur production dépasse 10 litres par semaine.</t>
   </si>
@@ -285,9 +276,6 @@
     <t>Village</t>
   </si>
   <si>
-    <t>Production (L)</t>
-  </si>
-  <si>
     <t>Prix/litre (DH)</t>
   </si>
   <si>
@@ -348,18 +336,6 @@
     <t>Souad Amghar</t>
   </si>
   <si>
-    <t>📊 BILAN DE LA COOPÉRATIVE</t>
-  </si>
-  <si>
-    <t>🎯 TRAVAIL À FAIRE :
-1️⃣ Revenu de base = Production × Prix
-2️⃣ Prime SI :         = si Revenu de base &gt;=10 ;  50DH   ;  0 DH
-3️⃣ Revenu total = Revenu base + Prime
-4️⃣ Si la prime passe à 100 DH pour ≥ 15 L, modifie la formule !
-5️⃣ Combien de productrices ont reçu une prime cette semaine ?
-6️⃣ Quelle est la production totale de la coopérative ?</t>
-  </si>
-  <si>
     <t>Production totale (L)</t>
   </si>
   <si>
@@ -382,6 +358,27 @@
   </si>
   <si>
     <t xml:space="preserve">Pourcentage Total </t>
+  </si>
+  <si>
+    <t>pourcentage %</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🌿 EXERCICE – Coopérative Arganière de Souss Massa | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fonction Si</t>
+    </r>
+  </si>
+  <si>
+    <t>Production (L)/semaine</t>
   </si>
 </sst>
 </file>
@@ -414,29 +411,9 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF375623"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -483,6 +460,26 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Sakkal Majalla"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -534,7 +531,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -582,86 +579,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -716,16 +633,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
+      <left style="thin">
         <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -734,129 +647,112 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -882,23 +778,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>167641</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>561570</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>83821</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1158240</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>78531</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 4">
+        <xdr:cNvPr id="2" name="Image 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9506D170-D936-4733-876A-53D82D324BAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1005A1D3-BB40-41F0-8A11-84EBD2433F1A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -907,7 +803,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -923,8 +819,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1958340" y="5524501"/>
-          <a:ext cx="1483590" cy="1531620"/>
+          <a:off x="4945380" y="4221481"/>
+          <a:ext cx="1013460" cy="1046270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -935,23 +831,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1241</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>493285</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 5">
+        <xdr:cNvPr id="3" name="Image 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC0EC912-C1DB-46DB-8424-23910CD77BC1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAD6713F-282D-4B9C-A4AA-63AB69C68BFD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -976,8 +872,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="266700" y="5585460"/>
-          <a:ext cx="1654781" cy="1181100"/>
+          <a:off x="6111240" y="4259580"/>
+          <a:ext cx="1377205" cy="982980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -989,22 +885,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>312420</xdr:rowOff>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>91441</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>109249</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:colOff>413062</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>85189</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="11" name="Groupe 10">
+        <xdr:cNvPr id="9" name="Groupe 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0EB02C2-2D57-34D4-6036-923C51F098C9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F9931FB-7684-977B-37A6-A8D562A3C902}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1012,10 +908,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9395460" y="312420"/>
-          <a:ext cx="3660169" cy="4099560"/>
-          <a:chOff x="10134600" y="784860"/>
-          <a:chExt cx="3660169" cy="4099560"/>
+          <a:off x="9631680" y="1104901"/>
+          <a:ext cx="3994462" cy="3666588"/>
+          <a:chOff x="9631680" y="1066801"/>
+          <a:chExt cx="3994462" cy="3666588"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
@@ -1023,7 +919,7 @@
           <xdr:cNvPr id="7" name="Image 6">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EF5E7B7-F3F9-8104-F6C7-47117CBE624B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA59692C-0430-996E-5B98-749873317794}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1039,8 +935,8 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="10134600" y="784860"/>
-            <a:ext cx="3660169" cy="2857500"/>
+            <a:off x="9631680" y="1066801"/>
+            <a:ext cx="3994462" cy="2613660"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1054,10 +950,10 @@
       </xdr:pic>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="10" name="Image 9">
+          <xdr:cNvPr id="8" name="Image 7">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC8A9D70-9A78-6FE8-660E-AA79A3E1E668}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85711295-4F4A-2CFF-0CEA-9A19FEF62719}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1073,8 +969,8 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="10165081" y="3680460"/>
-            <a:ext cx="3597462" cy="1203960"/>
+            <a:off x="9845041" y="3771901"/>
+            <a:ext cx="3665220" cy="961488"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -1270,92 +1166,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1C9A57-FDA2-41F8-9608-E611021D37BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67AB3D8-AF15-4C7C-8397-A8A2B570ECB5}">
   <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="5" width="14" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="11.88671875" customWidth="1"/>
     <col min="12" max="12" width="18.21875" customWidth="1"/>
     <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:11" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+    </row>
+    <row r="3" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-    </row>
-    <row r="3" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="5" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-    </row>
-    <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="I5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5">
         <v>12</v>
@@ -1363,25 +1268,30 @@
       <c r="E6" s="10">
         <v>350</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+    </row>
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>2</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6">
         <v>7</v>
@@ -1389,25 +1299,30 @@
       <c r="E7" s="12">
         <v>350</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+    </row>
+    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>3</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5">
         <v>15</v>
@@ -1415,25 +1330,30 @@
       <c r="E8" s="10">
         <v>350</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+    </row>
+    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>4</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" s="6">
         <v>9</v>
@@ -1441,25 +1361,30 @@
       <c r="E9" s="12">
         <v>350</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F9" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+    </row>
+    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>5</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D10" s="5">
         <v>11</v>
@@ -1467,25 +1392,30 @@
       <c r="E10" s="10">
         <v>350</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+    </row>
+    <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>6</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6">
         <v>6</v>
@@ -1493,25 +1423,30 @@
       <c r="E11" s="12">
         <v>350</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F11" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+    </row>
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>7</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" s="5">
         <v>14</v>
@@ -1519,25 +1454,30 @@
       <c r="E12" s="10">
         <v>350</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+    </row>
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>8</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13" s="7">
         <v>10</v>
@@ -1545,25 +1485,30 @@
       <c r="E13" s="12">
         <v>350</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>9</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" s="8">
         <v>8</v>
@@ -1571,25 +1516,30 @@
       <c r="E14" s="10">
         <v>350</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="F14" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+    </row>
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>10</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D15" s="7">
         <v>13</v>
@@ -1597,232 +1547,203 @@
       <c r="E15" s="12">
         <v>350</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="F15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K22" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
+      <c r="L22" s="26"/>
+      <c r="M22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32"/>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="32"/>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32"/>
-      <c r="K23" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="L23" s="20"/>
-      <c r="M23" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="35"/>
-      <c r="K24" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="2">
+      <c r="K23" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="22"/>
+      <c r="M23" s="2">
         <f>IF(AND(_xlfn.ISFORMULA(F6),F6=D6*E6),20%,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K25" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L25" s="16"/>
-      <c r="M25" s="2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K24" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="22"/>
+      <c r="M24" s="2">
         <f>IF(AND(_xlfn.ISFORMULA(G6),G6=(IF(D6&gt;=10,50,0))),20%,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K26" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="L26" s="16"/>
-      <c r="M26" s="2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K25" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="22"/>
+      <c r="M25" s="2">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(H6),H6=F6+G6),20%,0),0)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K26" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" s="22"/>
+      <c r="M26" s="2">
+        <f>IFERROR(IF(AND(_xlfn.ISFORMULA(I6),I6=H6/SUM($H$6:$H$15)),20%,0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K27" s="16" t="s">
+      <c r="K27" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="22"/>
+      <c r="M27" s="2">
+        <f>IFERROR(IF(AND(_xlfn.ISFORMULA(D17),D17=SUM(H6:H15)),5%,0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K28" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="22"/>
+      <c r="M28" s="2">
+        <f>IF(AND(_xlfn.ISFORMULA(D18),D18=SUM(D6:D15)),5%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K29" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" s="22"/>
+      <c r="M29" s="2">
+        <f>IF(AND(_xlfn.ISFORMULA(D19),D19=MAX(D6:D15)),5%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K30" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="22"/>
+      <c r="M30" s="2">
+        <f>IF(AND(_xlfn.ISFORMULA(D20),D20=MIN(D6:D15)),5%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K31" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="L27" s="16"/>
-      <c r="M27" s="2">
-        <f>IF(AND(_xlfn.ISFORMULA(D18),D18=SUM(D6:D15)),10%,0)</f>
+      <c r="L31" s="24"/>
+      <c r="M31" s="2">
+        <f>IF(AND(_xlfn.ISFORMULA(D21),D21=COUNT(D6:D15)),5%,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K28" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="16"/>
-      <c r="M28" s="2">
-        <f>IFERROR(IF(AND(_xlfn.ISFORMULA(D19),D19=SUM(H6:H15)),10%,0),0)</f>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K32" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" s="25"/>
+      <c r="M32" s="3">
+        <f>SUM(M23:M30)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K29" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="L29" s="16"/>
-      <c r="M29" s="2">
-        <f>IF(AND(_xlfn.ISFORMULA(D20),D20=MAX(D6:D15)),10%,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K30" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L30" s="16"/>
-      <c r="M30" s="2">
-        <f>IF(AND(_xlfn.ISFORMULA(D21),D21=MIN(D6:D15)),10%,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K31" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="L31" s="18"/>
-      <c r="M31" s="2">
-        <f>IF(AND(_xlfn.ISFORMULA(D22),D22=COUNT(D6:D15)),10%,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K32" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="L32" s="19"/>
-      <c r="M32" s="3">
-        <f>SUM(M24:M30)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:H24"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+  <mergeCells count="19">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K26:L26"/>
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="K30:L30"/>
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="K22:L22"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="K24:L24"/>
     <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K28:L28"/>
     <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
   </mergeCells>
-  <conditionalFormatting sqref="M24:M32">
+  <conditionalFormatting sqref="M23:M32">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1831,7 +1752,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1005E0B4-B28C-4D28-833F-717093B52A1F}</x14:id>
+          <x14:id>{9B0DA3BB-91BA-4315-84E6-F5C93FDC20C6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1844,7 +1765,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1005E0B4-B28C-4D28-833F-717093B52A1F}">
+          <x14:cfRule type="dataBar" id="{9B0DA3BB-91BA-4315-84E6-F5C93FDC20C6}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -1852,7 +1773,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M24:M32</xm:sqref>
+          <xm:sqref>M23:M32</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
